--- a/data/B_보고서_시트간검증/01_업무보고서_2025_3분기.xlsx
+++ b/data/B_보고서_시트간검증/01_업무보고서_2025_3분기.xlsx
@@ -11,8 +11,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="종목별" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부서별" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별추이" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계약명세" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성기준" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재보험자별" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지역별" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미수보험료" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정산내역" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계약명세" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성기준" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -538,6 +542,108 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>비율</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>백만원</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>작성일</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>작성부서</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>계리팀</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>손해율 정의</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>지급보험금 ÷ 수입보험료</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>전분기 대비 증감 정의</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(당분기 수입보험료 ÷ 전분기 수입보험료) - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>부서별 시트는 시스템에서 내려받아 그대로 붙였습니다</t>
         </is>
       </c>
     </row>
@@ -678,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -824,44 +930,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>계약번호</t>
+          <t>원수사</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>부서</t>
+          <t>수입보험료</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>종목</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>기준월</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>수입보험료</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>지급보험금</t>
         </is>
@@ -870,617 +958,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KR-3Q-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>국내특약부</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>화재</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1820</v>
-      </c>
-      <c r="F2" t="n">
-        <v>742</v>
+          <t>Nordic Re</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2630</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KR-3Q-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>국내특약부</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>화재</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>960</v>
-      </c>
-      <c r="F3" t="n">
-        <v>418</v>
+          <t>Pacific Rim</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5905</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2708</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KR-3Q-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>국내특약부</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>해상</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F4" t="n">
-        <v>655</v>
+          <t>남부생명</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6230</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2877</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KR-3Q-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>국내특약부</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>특종</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2150</v>
-      </c>
-      <c r="F5" t="n">
-        <v>980</v>
+          <t>대덕해상</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5320</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2322</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KR-3Q-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>국내특약부</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>화재</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1075</v>
-      </c>
-      <c r="F6" t="n">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KR-3Q-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>국내특약부</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>배상</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>840</v>
-      </c>
-      <c r="F7" t="n">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KR-3Q-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>국내특약부</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>해상</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1690</v>
-      </c>
-      <c r="F8" t="n">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>KR-3Q-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>국내특약부</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>특종</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>735</v>
-      </c>
-      <c r="F9" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>OS-3Q-101</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>해외재보험부</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>해상</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2480</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OS-3Q-102</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>해외재보험부</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>기술</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1130</v>
-      </c>
-      <c r="F11" t="n">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OS-3Q-103</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>해외재보험부</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>해상</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1975</v>
-      </c>
-      <c r="F12" t="n">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OS-3Q-104</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>해외재보험부</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>배상</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>620</v>
-      </c>
-      <c r="F13" t="n">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>OS-3Q-105</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>해외재보험부</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>기술</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F14" t="n">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OS-3Q-106</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>해외재보험부</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>해상</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>880</v>
-      </c>
-      <c r="F15" t="n">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SP-3Q-201</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>특종종목부</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>특종</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1340</v>
-      </c>
-      <c r="F16" t="n">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SP-3Q-202</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>특종종목부</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>기술</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>705</v>
-      </c>
-      <c r="F17" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SP-3Q-203</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>특종종목부</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>특종</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1620</v>
-      </c>
-      <c r="F18" t="n">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SP-3Q-204</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>특종종목부</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>배상</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>490</v>
-      </c>
-      <c r="F19" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SP-3Q-205</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>특종종목부</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>특종</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1185</v>
-      </c>
-      <c r="F20" t="n">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SP-3Q-206</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>특종종목부</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>기술</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>930</v>
-      </c>
-      <c r="F21" t="n">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SP-3Q-207</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>특종종목부</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>배상</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>560</v>
-      </c>
-      <c r="F22" t="n">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SP-3Q-205</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>특종종목부</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>특종</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1185</v>
-      </c>
-      <c r="F23" t="n">
-        <v>524</v>
+          <t>한강화재</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6975</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3279</v>
       </c>
     </row>
   </sheetData>
@@ -1494,83 +1031,1160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>항목</t>
+          <t>지역</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>내용</t>
+          <t>수입보험료</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>지급보험금</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>백만원</t>
-        </is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6975</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3279</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>작성일</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
+          <t>영남</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6230</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2877</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>작성부서</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>계리팀</t>
-        </is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8535</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4037</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>계약번호</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>미수액</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>경과일</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KR-3Q-004</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>180</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OS-3Q-103</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SP-3Q-203</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>240</v>
+      </c>
+      <c r="C4" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>손해율 정의</t>
+          <t>KR-3Q-009</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>정산차수</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>대상월</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>정산액</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>정산일</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3Q-1차</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4416</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3Q-2차</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4250</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3Q-3차</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3849</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>계약번호</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>원수사</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>기준월</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>수입보험료</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>지급보험금</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KR-3Q-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>국내특약부</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>한강화재</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>화재</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1820</v>
+      </c>
+      <c r="H2" t="n">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KR-3Q-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>국내특약부</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>대덕해상</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>충청</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>화재</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>960</v>
+      </c>
+      <c r="H3" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KR-3Q-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>국내특약부</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>한강화재</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>해상</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1240</v>
+      </c>
+      <c r="H4" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KR-3Q-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>지급보험금 ÷ 수입보험료</t>
-        </is>
+          <t>국내특약부</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>남부생명</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>영남</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>특종</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H5" t="n">
+        <v>980</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t>KR-3Q-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>부서별 시트는 시스템에서 내려받아 그대로 붙였습니다</t>
-        </is>
+          <t>국내특약부</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>대덕해상</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>충청</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>화재</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1075</v>
+      </c>
+      <c r="H6" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KR-3Q-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>국내특약부</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>한강화재</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>배상</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>840</v>
+      </c>
+      <c r="H7" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KR-3Q-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>국내특약부</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>남부생명</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>영남</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>해상</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1690</v>
+      </c>
+      <c r="H8" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KR-3Q-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>국내특약부</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>대덕해상</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>충청</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>특종</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>735</v>
+      </c>
+      <c r="H9" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OS-3Q-101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>해외재보험부</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pacific Rim</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>해상</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2480</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OS-3Q-102</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>해외재보험부</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nordic Re</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>기술</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1130</v>
+      </c>
+      <c r="H11" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OS-3Q-103</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>해외재보험부</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pacific Rim</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>해상</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1975</v>
+      </c>
+      <c r="H12" t="n">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OS-3Q-104</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>해외재보험부</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nordic Re</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>배상</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>620</v>
+      </c>
+      <c r="H13" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OS-3Q-105</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>해외재보험부</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pacific Rim</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>기술</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H14" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OS-3Q-106</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>해외재보험부</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nordic Re</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>해상</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>880</v>
+      </c>
+      <c r="H15" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SP-3Q-201</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>특종종목부</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>남부생명</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>영남</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>특종</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1340</v>
+      </c>
+      <c r="H16" t="n">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SP-3Q-202</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>특종종목부</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한강화재</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>기술</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>705</v>
+      </c>
+      <c r="H17" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SP-3Q-203</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>특종종목부</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>대덕해상</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>충청</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>특종</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1620</v>
+      </c>
+      <c r="H18" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SP-3Q-204</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>특종종목부</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>남부생명</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>영남</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>배상</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>490</v>
+      </c>
+      <c r="H19" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SP-3Q-205</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>특종종목부</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한강화재</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>특종</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1185</v>
+      </c>
+      <c r="H20" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SP-3Q-206</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>특종종목부</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>대덕해상</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>충청</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>기술</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>930</v>
+      </c>
+      <c r="H21" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SP-3Q-207</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>특종종목부</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>남부생명</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>영남</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>배상</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>560</v>
+      </c>
+      <c r="H22" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SP-3Q-205</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>특종종목부</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한강화재</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>특종</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1185</v>
+      </c>
+      <c r="H23" t="n">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
